--- a/data/trans_orig/IP35_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP35_2023-Estudios-trans_orig.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables originales" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2023" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q52"/>
+  <dimension ref="A1:W64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -524,12 +524,18 @@
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
     <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Progenitores según el nivel de estudios más alto finalizado en 2023 (Tasa respuesta: 99,95%)</t>
+          <t>Progenitores según el nivel de estudios más alto finalizado / solo 2023 en 2023 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -542,24 +548,30 @@
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="n"/>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="inlineStr">
         <is>
           <t>Niño</t>
         </is>
       </c>
-      <c r="I1" s="3" t="n"/>
-      <c r="J1" s="3" t="n"/>
       <c r="K1" s="3" t="n"/>
       <c r="L1" s="3" t="n"/>
-      <c r="M1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
+      <c r="M1" s="3" t="n"/>
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="3" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="n"/>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="n"/>
+      <c r="S1" s="3" t="n"/>
+      <c r="T1" s="3" t="n"/>
+      <c r="U1" s="3" t="n"/>
+      <c r="V1" s="3" t="n"/>
+      <c r="W1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -576,65 +588,95 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
+          <t>N (lím inf IC)</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>N (lím sup IC)</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
           <t>Estimación puntual</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>lím inf IC</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>n (muestra)</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>N (estimada)</t>
         </is>
       </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>N (lím inf IC)</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>N (lím sup IC)</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
         <is>
           <t>Estimación puntual</t>
         </is>
       </c>
-      <c r="K2" s="3" t="inlineStr">
+      <c r="O2" s="3" t="inlineStr">
         <is>
           <t>lím inf IC</t>
         </is>
       </c>
-      <c r="L2" s="3" t="inlineStr">
+      <c r="P2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
       </c>
-      <c r="M2" s="3" t="inlineStr">
+      <c r="Q2" s="3" t="inlineStr">
         <is>
           <t>n (muestra)</t>
         </is>
       </c>
-      <c r="N2" s="3" t="inlineStr">
+      <c r="R2" s="3" t="inlineStr">
         <is>
           <t>N (estimada)</t>
         </is>
       </c>
-      <c r="O2" s="3" t="inlineStr">
+      <c r="S2" s="3" t="inlineStr">
+        <is>
+          <t>N (lím inf IC)</t>
+        </is>
+      </c>
+      <c r="T2" s="3" t="inlineStr">
+        <is>
+          <t>N (lím sup IC)</t>
+        </is>
+      </c>
+      <c r="U2" s="3" t="inlineStr">
         <is>
           <t>Estimación puntual</t>
         </is>
       </c>
-      <c r="P2" s="3" t="inlineStr">
+      <c r="V2" s="3" t="inlineStr">
         <is>
           <t>lím inf IC</t>
         </is>
       </c>
-      <c r="Q2" s="3" t="inlineStr">
+      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
@@ -658,6 +700,12 @@
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
       <c r="Q3" s="2" t="n"/>
+      <c r="R3" s="2" t="n"/>
+      <c r="S3" s="2" t="n"/>
+      <c r="T3" s="2" t="n"/>
+      <c r="U3" s="2" t="n"/>
+      <c r="V3" s="2" t="n"/>
+      <c r="W3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -667,70 +715,112 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>ESO</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>0</v>
+          <t>Otros</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" s="2" t="n">
-        <v>0</v>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" s="2" t="n">
-        <v>0</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -738,70 +828,112 @@
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Otros estudios (especificar)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>0</v>
+          <t>Título de Doctorado</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="2" t="n">
-        <v>0</v>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" s="2" t="n">
-        <v>0</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -809,70 +941,112 @@
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Estudios universitarios de grado superior</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>0</v>
+          <t>Estudios universitarios de grado superior (Licenciados, másteres y especialidades en Ciencias de la Salud por el sistema</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="2" t="n">
-        <v>0</v>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" s="2" t="n">
-        <v>0</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -880,70 +1054,112 @@
       <c r="A7" s="1" t="n"/>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Estudios universitarios de grado medio</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>0</v>
+          <t>Estudios universitarios de grado medio (Diplomados/as universitarios/as, títulos propios universitarios de Experto o esp</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="2" t="n">
-        <v>0</v>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" s="2" t="n">
-        <v>0</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -951,70 +1167,112 @@
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estudios secundarios (BUP, B.Superior)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="2" t="n">
-        <v>0</v>
+          <t>Títulos propios de universidades de duración igual o superior a 2 años….</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="2" t="n">
-        <v>0</v>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" s="2" t="n">
-        <v>0</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1022,70 +1280,112 @@
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Estudios de FP II</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>0</v>
+          <t>Educación postsecundaria no superior</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="2" t="n">
-        <v>0</v>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" s="2" t="n">
-        <v>0</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1093,70 +1393,112 @@
       <c r="A10" s="1" t="n"/>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Estudios de FP I</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="2" t="n">
-        <v>0</v>
+          <t>Estudios secundarios (BUP, B.Superior, Bachillerato)</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" s="2" t="n">
-        <v>0</v>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" s="2" t="n">
-        <v>0</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1164,70 +1506,112 @@
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>EGB completa (8º) o similar (bachiller elemental)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="2" t="n">
-        <v>0</v>
+          <t>Estudios de FP II (Grado superior)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" s="2" t="n">
-        <v>0</v>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" s="2" t="n">
-        <v>0</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1235,70 +1619,112 @@
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Estudios primarios (hasta 5º EGB, ingreso)</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="n">
-        <v>53</v>
-      </c>
-      <c r="D12" s="2" t="n">
-        <v>44584</v>
+          <t>Estudios de FP I (Grado medio)</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>81,54%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>69,07%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>89,32%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="n">
-        <v>68</v>
-      </c>
-      <c r="I12" s="2" t="n">
-        <v>50960</v>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>82,19%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>71,23%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="n">
-        <v>121</v>
-      </c>
-      <c r="N12" s="2" t="n">
-        <v>95544</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>81,88%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>73,91%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>87,6%</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1306,70 +1732,112 @@
       <c r="A13" s="1" t="n"/>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>No ha estudiado pero sabe leer y escribir</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="D13" s="2" t="n">
-        <v>8590</v>
+          <t>ESO completa (Educación Secundaria Obligatoria)</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I13" s="2" t="n">
-        <v>8229</v>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="N13" s="2" t="n">
-        <v>16818</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1377,70 +1845,112 @@
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>No sabe leer o escribir</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D14" s="2" t="n">
-        <v>1504</v>
+          <t>EGB completa (8º) o similar (bachiller elemental)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="I14" s="2" t="n">
-        <v>2816</v>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="N14" s="2" t="n">
-        <v>4320</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1448,145 +1958,225 @@
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="n">
-        <v>69</v>
-      </c>
-      <c r="D15" s="2" t="n">
-        <v>54678</v>
+          <t>Estudios primarios (hasta 5º EGB, ingreso, educación primaria completa)</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>44584</t>
+        </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>38264</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>49081</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="n">
-        <v>83</v>
-      </c>
-      <c r="I15" s="2" t="n">
-        <v>62004</v>
+          <t>81,54%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>69,98%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>89,76%</t>
+        </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>68</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>50960</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="n">
-        <v>152</v>
-      </c>
-      <c r="N15" s="2" t="n">
-        <v>116682</v>
+          <t>44319</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>55549</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>82,19%</t>
+        </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>71,48%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>89,59%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>95544</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>85279</t>
+        </is>
+      </c>
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>102199</t>
+        </is>
+      </c>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>81,88%</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>73,09%</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>87,59%</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>Secundarios</t>
-        </is>
-      </c>
+      <c r="A16" s="1" t="n"/>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>ESO</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="n">
-        <v>148</v>
-      </c>
-      <c r="D16" s="2" t="n">
-        <v>121501</v>
+          <t>No ha estudiado pero sabe leer y escribir</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>8590</t>
+        </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>4725</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>15233</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>41,13%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="n">
-        <v>147</v>
-      </c>
-      <c r="I16" s="2" t="n">
-        <v>115042</v>
+          <t>15,71%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>8,64%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>27,86%</t>
+        </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>8229</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="n">
-        <v>295</v>
-      </c>
-      <c r="N16" s="2" t="n">
-        <v>236543</v>
+          <t>4108</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>15002</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>13,27%</t>
+        </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>16818</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>11155</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>27249</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>14,41%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>9,56%</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>23,35%</t>
         </is>
       </c>
     </row>
@@ -1594,70 +2184,112 @@
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Otros estudios (especificar)</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="D17" s="2" t="n">
-        <v>1387</v>
+          <t>No sabe leer o escribir</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>1504</t>
+        </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>4850</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="I17" s="2" t="n">
-        <v>5754</v>
+          <t>2,75%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>8,87%</t>
+        </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>2816</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="N17" s="2" t="n">
-        <v>7141</v>
+          <t>957</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>6601</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>4,54%</t>
+        </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>4320</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>1677</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>9014</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>3,7%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>1,44%</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>7,73%</t>
         </is>
       </c>
     </row>
@@ -1665,127 +2297,185 @@
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Estudios universitarios de grado superior</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" s="2" t="n">
-        <v>0</v>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>54678</t>
+        </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>54678</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>54678</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" s="2" t="n">
-        <v>0</v>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>83</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>62004</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" s="2" t="n">
-        <v>0</v>
+          <t>62004</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>62004</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>116682</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>116682</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>116682</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n"/>
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Estudios universitarios de grado medio</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" s="2" t="n">
-        <v>0</v>
+          <t>Otros</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>492</t>
+        </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>2776</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" s="2" t="n">
-        <v>0</v>
+          <t>0,11%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>868</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" s="2" t="n">
-        <v>0</v>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>4444</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>0,17%</t>
+        </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
@@ -1794,12 +2484,42 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>1360</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>4871</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>0,14%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
         </is>
       </c>
     </row>
@@ -1807,70 +2527,112 @@
       <c r="A20" s="1" t="n"/>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Estudios secundarios (BUP, B.Superior)</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="n">
-        <v>140</v>
-      </c>
-      <c r="D20" s="2" t="n">
-        <v>93255</v>
+          <t>Título de Doctorado</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="n">
-        <v>109</v>
-      </c>
-      <c r="I20" s="2" t="n">
-        <v>83651</v>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="n">
-        <v>249</v>
-      </c>
-      <c r="N20" s="2" t="n">
-        <v>176906</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1878,70 +2640,112 @@
       <c r="A21" s="1" t="n"/>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Estudios de FP II</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="n">
-        <v>110</v>
-      </c>
-      <c r="D21" s="2" t="n">
-        <v>79166</v>
+          <t>Estudios universitarios de grado superior (Licenciados, másteres y especialidades en Ciencias de la Salud por el sistema</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="n">
-        <v>98</v>
-      </c>
-      <c r="I21" s="2" t="n">
-        <v>72992</v>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="n">
-        <v>208</v>
-      </c>
-      <c r="N21" s="2" t="n">
-        <v>152158</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1949,70 +2753,112 @@
       <c r="A22" s="1" t="n"/>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Estudios de FP I</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="n">
-        <v>62</v>
-      </c>
-      <c r="D22" s="2" t="n">
-        <v>40816</v>
+          <t>Estudios universitarios de grado medio (Diplomados/as universitarios/as, títulos propios universitarios de Experto o esp</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="n">
-        <v>95</v>
-      </c>
-      <c r="I22" s="2" t="n">
-        <v>67903</v>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="n">
-        <v>157</v>
-      </c>
-      <c r="N22" s="2" t="n">
-        <v>108720</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2020,70 +2866,112 @@
       <c r="A23" s="1" t="n"/>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>EGB completa (8º) o similar (bachiller elemental)</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="n">
-        <v>171</v>
-      </c>
-      <c r="D23" s="2" t="n">
-        <v>118565</v>
+          <t>Títulos propios de universidades de duración igual o superior a 2 años….</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="n">
-        <v>187</v>
-      </c>
-      <c r="I23" s="2" t="n">
-        <v>161192</v>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="n">
-        <v>358</v>
-      </c>
-      <c r="N23" s="2" t="n">
-        <v>279756</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2091,70 +2979,112 @@
       <c r="A24" s="1" t="n"/>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Estudios primarios (hasta 5º EGB, ingreso)</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="D24" s="2" t="n">
-        <v>3426</v>
+          <t>Educación postsecundaria no superior</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>896</t>
+        </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>3316</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="I24" s="2" t="n">
-        <v>7795</v>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>0,72%</t>
+        </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>4886</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="N24" s="2" t="n">
-        <v>11221</v>
+          <t>2061</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>9087</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>0,95%</t>
+        </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>5782</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>3012</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>10856</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>0,59%</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>0,31%</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>1,11%</t>
         </is>
       </c>
     </row>
@@ -2162,70 +3092,112 @@
       <c r="A25" s="1" t="n"/>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>No ha estudiado pero sabe leer y escribir</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="D25" s="2" t="n">
-        <v>1902</v>
+          <t>Estudios secundarios (BUP, B.Superior, Bachillerato)</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>93255</t>
+        </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>74764</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>110219</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I25" s="2" t="n">
-        <v>1717</v>
+          <t>20,25%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>16,24%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>23,93%</t>
+        </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>109</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>83651</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="N25" s="2" t="n">
-        <v>3618</v>
+          <t>66700</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>101258</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>16,19%</t>
+        </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>249</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>176906</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>152794</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>203329</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>18,1%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>15,64%</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>20,81%</t>
         </is>
       </c>
     </row>
@@ -2233,70 +3205,112 @@
       <c r="A26" s="1" t="n"/>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>No sabe leer o escribir</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D26" s="2" t="n">
-        <v>492</v>
+          <t>Estudios de FP II (Grado superior)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>79166</t>
+        </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>63443</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>96976</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I26" s="2" t="n">
-        <v>573</v>
+          <t>17,19%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>13,78%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>21,06%</t>
+        </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>98</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>72992</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="N26" s="2" t="n">
-        <v>1064</v>
+          <t>57186</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>91783</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>14,13%</t>
+        </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>152158</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>129588</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>174989</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>15,57%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>13,26%</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>17,91%</t>
         </is>
       </c>
     </row>
@@ -2304,145 +3318,225 @@
       <c r="A27" s="1" t="n"/>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="n">
-        <v>643</v>
-      </c>
-      <c r="D27" s="2" t="n">
-        <v>460510</v>
+          <t>Estudios de FP I (Grado medio)</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>40816</t>
+        </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>30529</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>53059</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="n">
-        <v>656</v>
-      </c>
-      <c r="I27" s="2" t="n">
-        <v>516619</v>
+          <t>8,86%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>6,63%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>11,52%</t>
+        </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>95</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>67903</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="n">
-        <v>1299</v>
-      </c>
-      <c r="N27" s="2" t="n">
-        <v>977129</v>
+          <t>55434</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>83428</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>13,14%</t>
+        </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t>108720</t>
+        </is>
+      </c>
+      <c r="S27" s="2" t="inlineStr">
+        <is>
+          <t>91439</t>
+        </is>
+      </c>
+      <c r="T27" s="2" t="inlineStr">
+        <is>
+          <t>128200</t>
+        </is>
+      </c>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>11,13%</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>9,36%</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>13,12%</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A28" s="1" t="n"/>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>ESO</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D28" s="2" t="n">
-        <v>0</v>
+          <t>ESO completa (Educación Secundaria Obligatoria)</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>121501</t>
+        </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>94082</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>192273</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I28" s="2" t="n">
-        <v>851</v>
+          <t>26,38%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>20,43%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>41,75%</t>
+        </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>147</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>115042</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N28" s="2" t="n">
-        <v>851</v>
+          <t>94979</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>147654</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>22,27%</t>
+        </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>28,58%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>295</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>236543</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>201609</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>306161</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>24,21%</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>20,63%</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>31,33%</t>
         </is>
       </c>
     </row>
@@ -2450,70 +3544,112 @@
       <c r="A29" s="1" t="n"/>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Otros estudios (especificar)</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="D29" s="2" t="n">
-        <v>14378</v>
+          <t>EGB completa (8º) o similar (bachiller elemental)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>118565</t>
+        </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>92838</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>136126</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="I29" s="2" t="n">
-        <v>19260</v>
+          <t>25,75%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>20,16%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>29,56%</t>
+        </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>187</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>161192</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="n">
-        <v>53</v>
-      </c>
-      <c r="N29" s="2" t="n">
-        <v>33638</v>
+          <t>138130</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>184171</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>31,2%</t>
+        </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>26,74%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>35,65%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>358</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>279756</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>251541</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>311643</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>28,63%</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>25,74%</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>31,89%</t>
         </is>
       </c>
     </row>
@@ -2521,70 +3657,112 @@
       <c r="A30" s="1" t="n"/>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Estudios universitarios de grado superior</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="n">
-        <v>115</v>
-      </c>
-      <c r="D30" s="2" t="n">
-        <v>79122</v>
+          <t>Estudios primarios (hasta 5º EGB, ingreso, educación primaria completa)</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>3426</t>
+        </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>52,91%</t>
+          <t>1260</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>45,18%</t>
+          <t>8067</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>59,28%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="n">
-        <v>127</v>
-      </c>
-      <c r="I30" s="2" t="n">
-        <v>103094</v>
+          <t>0,74%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>1,75%</t>
+        </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>56,23%</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>49,23%</t>
+          <t>7795</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>62,61%</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="n">
-        <v>242</v>
-      </c>
-      <c r="N30" s="2" t="n">
-        <v>182216</v>
+          <t>3385</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>16117</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>1,51%</t>
+        </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>54,74%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>50,38%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t>59,41%</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>11221</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>6018</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>20289</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>1,15%</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>0,62%</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -2592,70 +3770,112 @@
       <c r="A31" s="1" t="n"/>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Estudios universitarios de grado medio</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="n">
-        <v>83</v>
-      </c>
-      <c r="D31" s="2" t="n">
-        <v>52894</v>
+          <t>No ha estudiado pero sabe leer y escribir</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>1902</t>
+        </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>35,37%</t>
+          <t>497</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>5397</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>42,08%</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="n">
-        <v>82</v>
-      </c>
-      <c r="I31" s="2" t="n">
-        <v>58539</v>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>0,11%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>1,17%</t>
+        </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>1717</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>38,48%</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="n">
-        <v>165</v>
-      </c>
-      <c r="N31" s="2" t="n">
-        <v>111433</v>
+          <t>352</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>4996</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>0,33%</t>
+        </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>3618</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>1377</t>
+        </is>
+      </c>
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t>8370</t>
+        </is>
+      </c>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>0,14%</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>0,86%</t>
         </is>
       </c>
     </row>
@@ -2663,70 +3883,112 @@
       <c r="A32" s="1" t="n"/>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Estudios secundarios (BUP, B.Superior)</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D32" s="2" t="n">
-        <v>0</v>
+          <t>No sabe leer o escribir</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>492</t>
+        </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>2091</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="I32" s="2" t="n">
-        <v>1605</v>
+          <t>0,11%</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>0,45%</t>
+        </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>573</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="N32" s="2" t="n">
-        <v>1605</v>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>2914</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>0,11%</t>
+        </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>1064</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>3541</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>0,11%</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>0,36%</t>
         </is>
       </c>
     </row>
@@ -2734,141 +3996,229 @@
       <c r="A33" s="1" t="n"/>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Estudios de FP II</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D33" s="2" t="n">
-        <v>566</v>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>643</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>460510</t>
+        </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>460510</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>460510</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" s="2" t="n">
-        <v>0</v>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>656</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>516619</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N33" s="2" t="n">
-        <v>566</v>
+          <t>516619</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>516619</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>1299</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr">
+        <is>
+          <t>977129</t>
+        </is>
+      </c>
+      <c r="S33" s="2" t="inlineStr">
+        <is>
+          <t>977129</t>
+        </is>
+      </c>
+      <c r="T33" s="2" t="inlineStr">
+        <is>
+          <t>977129</t>
+        </is>
+      </c>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n"/>
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Estudios de FP I</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D34" s="2" t="n">
-        <v>0</v>
+          <t>Otros</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" s="2" t="n">
-        <v>0</v>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" s="2" t="n">
-        <v>0</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2876,70 +4226,112 @@
       <c r="A35" s="1" t="n"/>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>EGB completa (8º) o similar (bachiller elemental)</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="D35" s="2" t="n">
-        <v>1853</v>
+          <t>Título de Doctorado</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>3352</t>
+        </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1291</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>7691</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" s="2" t="n">
-        <v>0</v>
+          <t>2,24%</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>0,86%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>5,14%</t>
+        </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>3792</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="N35" s="2" t="n">
-        <v>1853</v>
+          <t>1277</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>9376</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>2,07%</t>
+        </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t>7145</t>
+        </is>
+      </c>
+      <c r="S35" s="2" t="inlineStr">
+        <is>
+          <t>3675</t>
+        </is>
+      </c>
+      <c r="T35" s="2" t="inlineStr">
+        <is>
+          <t>12999</t>
+        </is>
+      </c>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>2,15%</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>1,1%</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>3,9%</t>
         </is>
       </c>
     </row>
@@ -2947,70 +4339,112 @@
       <c r="A36" s="1" t="n"/>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Estudios primarios (hasta 5º EGB, ingreso)</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D36" s="2" t="n">
-        <v>738</v>
+          <t>Estudios universitarios de grado superior (Licenciados, másteres y especialidades en Ciencias de la Salud por el sistema</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>79122</t>
+        </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>68488</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>89164</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" s="2" t="n">
-        <v>0</v>
+          <t>52,91%</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>45,8%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>59,62%</t>
+        </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>127</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>103094</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N36" s="2" t="n">
-        <v>738</v>
+          <t>91979</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>115436</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>56,23%</t>
+        </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>50,17%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>62,96%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>182216</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t>164459</t>
+        </is>
+      </c>
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t>196065</t>
+        </is>
+      </c>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>54,74%</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>49,4%</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>58,9%</t>
         </is>
       </c>
     </row>
@@ -3018,70 +4452,112 @@
       <c r="A37" s="1" t="n"/>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>No ha estudiado pero sabe leer y escribir</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D37" s="2" t="n">
-        <v>0</v>
+          <t>Estudios universitarios de grado medio (Diplomados/as universitarios/as, títulos propios universitarios de Experto o esp</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>52894</t>
+        </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>43353</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>63422</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" s="2" t="n">
-        <v>0</v>
+          <t>35,37%</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>28,99%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>42,41%</t>
+        </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>82</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>58539</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N37" s="2" t="n">
-        <v>0</v>
+          <t>47241</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>69005</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>31,93%</t>
+        </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>37,64%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>111433</t>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t>97431</t>
+        </is>
+      </c>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>126620</t>
+        </is>
+      </c>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>33,47%</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>29,27%</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>38,04%</t>
         </is>
       </c>
     </row>
@@ -3089,70 +4565,112 @@
       <c r="A38" s="1" t="n"/>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>No sabe leer o escribir</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D38" s="2" t="n">
-        <v>0</v>
+          <t>Títulos propios de universidades de duración igual o superior a 2 años….</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>11026</t>
+        </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7041</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>16778</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" s="2" t="n">
-        <v>0</v>
+          <t>7,37%</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>4,71%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>11,22%</t>
+        </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>14895</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N38" s="2" t="n">
-        <v>0</v>
+          <t>9109</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>22145</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>8,12%</t>
+        </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t>25921</t>
+        </is>
+      </c>
+      <c r="S38" s="2" t="inlineStr">
+        <is>
+          <t>18951</t>
+        </is>
+      </c>
+      <c r="T38" s="2" t="inlineStr">
+        <is>
+          <t>34663</t>
+        </is>
+      </c>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>7,79%</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>5,69%</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>10,41%</t>
         </is>
       </c>
     </row>
@@ -3160,145 +4678,225 @@
       <c r="A39" s="1" t="n"/>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="n">
-        <v>230</v>
-      </c>
-      <c r="D39" s="2" t="n">
-        <v>149551</v>
+          <t>Educación postsecundaria no superior</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="n">
-        <v>238</v>
-      </c>
-      <c r="I39" s="2" t="n">
-        <v>183349</v>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>573</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="n">
-        <v>468</v>
-      </c>
-      <c r="N39" s="2" t="n">
-        <v>332900</v>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>3452</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>0,31%</t>
+        </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr">
+        <is>
+          <t>573</t>
+        </is>
+      </c>
+      <c r="S39" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T39" s="2" t="inlineStr">
+        <is>
+          <t>2874</t>
+        </is>
+      </c>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>0,86%</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
+      <c r="A40" s="1" t="n"/>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>ESO</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="n">
-        <v>148</v>
-      </c>
-      <c r="D40" s="2" t="n">
-        <v>121501</v>
+          <t>Estudios secundarios (BUP, B.Superior, Bachillerato)</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="n">
-        <v>148</v>
-      </c>
-      <c r="I40" s="2" t="n">
-        <v>115893</v>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>1605</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="n">
-        <v>296</v>
-      </c>
-      <c r="N40" s="2" t="n">
-        <v>237394</v>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>5400</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>0,88%</t>
+        </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t>1605</t>
+        </is>
+      </c>
+      <c r="S40" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T40" s="2" t="inlineStr">
+        <is>
+          <t>5745</t>
+        </is>
+      </c>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>0,48%</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -3306,70 +4904,112 @@
       <c r="A41" s="1" t="n"/>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Otros estudios (especificar)</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="D41" s="2" t="n">
-        <v>15765</v>
+          <t>Estudios de FP II (Grado superior)</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>566</t>
+        </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>3331</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="I41" s="2" t="n">
-        <v>25015</v>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>2,23%</t>
+        </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="N41" s="2" t="n">
-        <v>40780</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t>566</t>
+        </is>
+      </c>
+      <c r="S41" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T41" s="2" t="inlineStr">
+        <is>
+          <t>3507</t>
+        </is>
+      </c>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -3377,70 +5017,112 @@
       <c r="A42" s="1" t="n"/>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Estudios universitarios de grado superior</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="n">
-        <v>115</v>
-      </c>
-      <c r="D42" s="2" t="n">
-        <v>79122</v>
+          <t>Estudios de FP I (Grado medio)</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="n">
-        <v>127</v>
-      </c>
-      <c r="I42" s="2" t="n">
-        <v>103093</v>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="n">
-        <v>242</v>
-      </c>
-      <c r="N42" s="2" t="n">
-        <v>182216</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S42" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T42" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3448,70 +5130,112 @@
       <c r="A43" s="1" t="n"/>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Estudios universitarios de grado medio</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="n">
-        <v>83</v>
-      </c>
-      <c r="D43" s="2" t="n">
-        <v>52894</v>
+          <t>ESO completa (Educación Secundaria Obligatoria)</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="n">
-        <v>82</v>
-      </c>
-      <c r="I43" s="2" t="n">
-        <v>58539</v>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>851</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="n">
-        <v>165</v>
-      </c>
-      <c r="N43" s="2" t="n">
-        <v>111433</v>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>4351</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>0,46%</t>
+        </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t>851</t>
+        </is>
+      </c>
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T43" s="2" t="inlineStr">
+        <is>
+          <t>4276</t>
+        </is>
+      </c>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>0,26%</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>1,28%</t>
         </is>
       </c>
     </row>
@@ -3519,70 +5243,112 @@
       <c r="A44" s="1" t="n"/>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Estudios secundarios (BUP, B.Superior)</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="n">
-        <v>140</v>
-      </c>
-      <c r="D44" s="2" t="n">
-        <v>93255</v>
+          <t>EGB completa (8º) o similar (bachiller elemental)</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>1853</t>
+        </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>512</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>5581</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="n">
-        <v>111</v>
-      </c>
-      <c r="I44" s="2" t="n">
-        <v>85256</v>
+          <t>1,24%</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>0,34%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>3,73%</t>
+        </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="n">
-        <v>251</v>
-      </c>
-      <c r="N44" s="2" t="n">
-        <v>178511</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr">
+        <is>
+          <t>1853</t>
+        </is>
+      </c>
+      <c r="S44" s="2" t="inlineStr">
+        <is>
+          <t>512</t>
+        </is>
+      </c>
+      <c r="T44" s="2" t="inlineStr">
+        <is>
+          <t>5561</t>
+        </is>
+      </c>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>0,56%</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>0,15%</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -3590,70 +5356,112 @@
       <c r="A45" s="1" t="n"/>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>Estudios de FP II</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="n">
-        <v>111</v>
-      </c>
-      <c r="D45" s="2" t="n">
-        <v>79731</v>
+          <t>Estudios primarios (hasta 5º EGB, ingreso, educación primaria completa)</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>738</t>
+        </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>3671</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="n">
-        <v>98</v>
-      </c>
-      <c r="I45" s="2" t="n">
-        <v>72992</v>
+          <t>0,49%</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>2,45%</t>
+        </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="n">
-        <v>209</v>
-      </c>
-      <c r="N45" s="2" t="n">
-        <v>152724</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr">
+        <is>
+          <t>738</t>
+        </is>
+      </c>
+      <c r="S45" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T45" s="2" t="inlineStr">
+        <is>
+          <t>3619</t>
+        </is>
+      </c>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>1,09%</t>
         </is>
       </c>
     </row>
@@ -3661,70 +5469,112 @@
       <c r="A46" s="1" t="n"/>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Estudios de FP I</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="n">
-        <v>62</v>
-      </c>
-      <c r="D46" s="2" t="n">
-        <v>40816</v>
+          <t>No ha estudiado pero sabe leer y escribir</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="n">
-        <v>95</v>
-      </c>
-      <c r="I46" s="2" t="n">
-        <v>67903</v>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="n">
-        <v>157</v>
-      </c>
-      <c r="N46" s="2" t="n">
-        <v>108720</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S46" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T46" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3732,70 +5582,112 @@
       <c r="A47" s="1" t="n"/>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>EGB completa (8º) o similar (bachiller elemental)</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="n">
-        <v>174</v>
-      </c>
-      <c r="D47" s="2" t="n">
-        <v>120417</v>
+          <t>No sabe leer o escribir</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="n">
-        <v>187</v>
-      </c>
-      <c r="I47" s="2" t="n">
-        <v>161192</v>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="n">
-        <v>361</v>
-      </c>
-      <c r="N47" s="2" t="n">
-        <v>281609</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S47" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T47" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3803,141 +5695,229 @@
       <c r="A48" s="1" t="n"/>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Estudios primarios (hasta 5º EGB, ingreso)</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="n">
-        <v>59</v>
-      </c>
-      <c r="D48" s="2" t="n">
-        <v>48748</v>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>149551</t>
+        </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>149551</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>149551</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="n">
-        <v>75</v>
-      </c>
-      <c r="I48" s="2" t="n">
-        <v>58755</v>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>238</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>183349</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="n">
-        <v>134</v>
-      </c>
-      <c r="N48" s="2" t="n">
-        <v>107503</v>
+          <t>183349</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>183349</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>468</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="inlineStr">
+        <is>
+          <t>332900</t>
+        </is>
+      </c>
+      <c r="S48" s="2" t="inlineStr">
+        <is>
+          <t>332900</t>
+        </is>
+      </c>
+      <c r="T48" s="2" t="inlineStr">
+        <is>
+          <t>332900</t>
+        </is>
+      </c>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n"/>
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>No ha estudiado pero sabe leer y escribir</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="D49" s="2" t="n">
-        <v>10492</v>
+          <t>Otros</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>492</t>
+        </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>2582</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
-        </is>
-      </c>
-      <c r="H49" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="I49" s="2" t="n">
-        <v>9945</v>
+          <t>0,07%</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>0,39%</t>
+        </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>868</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="N49" s="2" t="n">
-        <v>20437</v>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>4361</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>0,11%</t>
+        </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R49" s="2" t="inlineStr">
+        <is>
+          <t>1360</t>
+        </is>
+      </c>
+      <c r="S49" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T49" s="2" t="inlineStr">
+        <is>
+          <t>5377</t>
+        </is>
+      </c>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>0,1%</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
         </is>
       </c>
     </row>
@@ -3945,70 +5925,112 @@
       <c r="A50" s="1" t="n"/>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>No sabe leer o escribir</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="D50" s="2" t="n">
-        <v>1996</v>
+          <t>Título de Doctorado</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>3352</t>
+        </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>1161</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>7525</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="I50" s="2" t="n">
-        <v>3388</v>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>1,13%</t>
+        </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>3792</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="N50" s="2" t="n">
-        <v>5384</v>
+          <t>1169</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>9088</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R50" s="2" t="inlineStr">
+        <is>
+          <t>7145</t>
+        </is>
+      </c>
+      <c r="S50" s="2" t="inlineStr">
+        <is>
+          <t>3599</t>
+        </is>
+      </c>
+      <c r="T50" s="2" t="inlineStr">
+        <is>
+          <t>12874</t>
+        </is>
+      </c>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>0,25%</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>0,9%</t>
         </is>
       </c>
     </row>
@@ -4016,75 +6038,1473 @@
       <c r="A51" s="1" t="n"/>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="n">
-        <v>942</v>
-      </c>
-      <c r="D51" s="2" t="n">
-        <v>664738</v>
+          <t>Estudios universitarios de grado superior (Licenciados, másteres y especialidades en Ciencias de la Salud por el sistema</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>79122</t>
+        </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>64303</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>95848</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H51" s="2" t="n">
-        <v>977</v>
-      </c>
-      <c r="I51" s="2" t="n">
-        <v>761972</v>
+          <t>11,9%</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>9,67%</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>14,42%</t>
+        </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>127</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>103093</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="n">
-        <v>1919</v>
-      </c>
-      <c r="N51" s="2" t="n">
-        <v>1426710</v>
+          <t>85977</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>126235</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>13,53%</t>
+        </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="R51" s="2" t="inlineStr">
+        <is>
+          <t>182216</t>
+        </is>
+      </c>
+      <c r="S51" s="2" t="inlineStr">
+        <is>
+          <t>157042</t>
+        </is>
+      </c>
+      <c r="T51" s="2" t="inlineStr">
+        <is>
+          <t>206400</t>
+        </is>
+      </c>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>12,77%</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>11,01%</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>14,47%</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
+      <c r="A52" s="1" t="n"/>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>Estudios universitarios de grado medio (Diplomados/as universitarios/as, títulos propios universitarios de Experto o esp</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>52894</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>41326</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>66081</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>7,96%</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>6,22%</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>9,94%</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>58539</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>46768</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>74403</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>7,68%</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>6,14%</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>9,76%</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="inlineStr">
+        <is>
+          <t>111433</t>
+        </is>
+      </c>
+      <c r="S52" s="2" t="inlineStr">
+        <is>
+          <t>94889</t>
+        </is>
+      </c>
+      <c r="T52" s="2" t="inlineStr">
+        <is>
+          <t>131304</t>
+        </is>
+      </c>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>7,81%</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>6,65%</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>9,2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="n"/>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>Títulos propios de universidades de duración igual o superior a 2 años….</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>11026</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>6945</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>17458</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>1,66%</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>1,04%</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>2,63%</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>14895</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>8854</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>23196</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>1,95%</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>1,16%</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>3,04%</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="R53" s="2" t="inlineStr">
+        <is>
+          <t>25921</t>
+        </is>
+      </c>
+      <c r="S53" s="2" t="inlineStr">
+        <is>
+          <t>18633</t>
+        </is>
+      </c>
+      <c r="T53" s="2" t="inlineStr">
+        <is>
+          <t>36972</t>
+        </is>
+      </c>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>1,82%</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>1,31%</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>2,59%</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="n"/>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>Educación postsecundaria no superior</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>896</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>3182</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>0,13%</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>0,48%</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>5459</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>2638</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>10593</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>0,72%</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>1,39%</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R54" s="2" t="inlineStr">
+        <is>
+          <t>6355</t>
+        </is>
+      </c>
+      <c r="S54" s="2" t="inlineStr">
+        <is>
+          <t>3297</t>
+        </is>
+      </c>
+      <c r="T54" s="2" t="inlineStr">
+        <is>
+          <t>11672</t>
+        </is>
+      </c>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>0,45%</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>0,23%</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>0,82%</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="n"/>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>Estudios secundarios (BUP, B.Superior, Bachillerato)</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>93255</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>77009</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>111011</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>14,03%</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>11,58%</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>16,7%</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>85256</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>70363</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>104241</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>11,19%</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>9,23%</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>13,68%</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr">
+        <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="R55" s="2" t="inlineStr">
+        <is>
+          <t>178511</t>
+        </is>
+      </c>
+      <c r="S55" s="2" t="inlineStr">
+        <is>
+          <t>154625</t>
+        </is>
+      </c>
+      <c r="T55" s="2" t="inlineStr">
+        <is>
+          <t>203407</t>
+        </is>
+      </c>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>12,51%</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>10,84%</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>14,26%</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="n"/>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>Estudios de FP II (Grado superior)</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>79731</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>63604</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>96272</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>11,99%</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>9,57%</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>14,48%</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>72992</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>60125</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>92968</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>9,58%</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>7,89%</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>12,2%</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="R56" s="2" t="inlineStr">
+        <is>
+          <t>152724</t>
+        </is>
+      </c>
+      <c r="S56" s="2" t="inlineStr">
+        <is>
+          <t>131214</t>
+        </is>
+      </c>
+      <c r="T56" s="2" t="inlineStr">
+        <is>
+          <t>177486</t>
+        </is>
+      </c>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>10,7%</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>9,2%</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>12,44%</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="n"/>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>Estudios de FP I (Grado medio)</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>40816</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>29735</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>51794</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>6,14%</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>4,47%</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>7,79%</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>67903</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>54608</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>84434</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>8,91%</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>7,17%</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>11,08%</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="R57" s="2" t="inlineStr">
+        <is>
+          <t>108720</t>
+        </is>
+      </c>
+      <c r="S57" s="2" t="inlineStr">
+        <is>
+          <t>91750</t>
+        </is>
+      </c>
+      <c r="T57" s="2" t="inlineStr">
+        <is>
+          <t>127591</t>
+        </is>
+      </c>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>7,62%</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>6,43%</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>8,94%</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="n"/>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>ESO completa (Educación Secundaria Obligatoria)</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>121501</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>92745</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>195311</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>18,28%</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>13,95%</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>29,38%</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>115893</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>93957</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>151219</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>15,21%</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>12,33%</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>19,85%</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr">
+        <is>
+          <t>296</t>
+        </is>
+      </c>
+      <c r="R58" s="2" t="inlineStr">
+        <is>
+          <t>237394</t>
+        </is>
+      </c>
+      <c r="S58" s="2" t="inlineStr">
+        <is>
+          <t>199766</t>
+        </is>
+      </c>
+      <c r="T58" s="2" t="inlineStr">
+        <is>
+          <t>323799</t>
+        </is>
+      </c>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>16,64%</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>14,0%</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>22,7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="n"/>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>EGB completa (8º) o similar (bachiller elemental)</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>120417</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>99893</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>138091</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>18,12%</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>15,03%</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>20,77%</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>161192</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>138180</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>183911</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>21,15%</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>18,13%</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>24,14%</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr">
+        <is>
+          <t>361</t>
+        </is>
+      </c>
+      <c r="R59" s="2" t="inlineStr">
+        <is>
+          <t>281609</t>
+        </is>
+      </c>
+      <c r="S59" s="2" t="inlineStr">
+        <is>
+          <t>251117</t>
+        </is>
+      </c>
+      <c r="T59" s="2" t="inlineStr">
+        <is>
+          <t>313341</t>
+        </is>
+      </c>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>19,74%</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>17,6%</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>21,96%</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="n"/>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>Estudios primarios (hasta 5º EGB, ingreso, educación primaria completa)</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>48748</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>36365</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>72500</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>7,33%</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>5,47%</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>10,91%</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>58755</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>46947</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>73989</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>7,71%</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>6,16%</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>9,71%</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="R60" s="2" t="inlineStr">
+        <is>
+          <t>107503</t>
+        </is>
+      </c>
+      <c r="S60" s="2" t="inlineStr">
+        <is>
+          <t>88996</t>
+        </is>
+      </c>
+      <c r="T60" s="2" t="inlineStr">
+        <is>
+          <t>133332</t>
+        </is>
+      </c>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>7,54%</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>6,24%</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>9,35%</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="n"/>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>No ha estudiado pero sabe leer y escribir</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>10492</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>5982</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>16878</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>1,58%</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>0,9%</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>2,54%</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>9945</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>5387</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>18568</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>1,31%</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>0,71%</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>2,44%</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="R61" s="2" t="inlineStr">
+        <is>
+          <t>20437</t>
+        </is>
+      </c>
+      <c r="S61" s="2" t="inlineStr">
+        <is>
+          <t>13912</t>
+        </is>
+      </c>
+      <c r="T61" s="2" t="inlineStr">
+        <is>
+          <t>30894</t>
+        </is>
+      </c>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>1,43%</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>0,98%</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>2,17%</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="n"/>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>No sabe leer o escribir</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>496</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>5544</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>0,07%</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>0,83%</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>3388</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>1206</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>7591</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>0,16%</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>1,0%</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R62" s="2" t="inlineStr">
+        <is>
+          <t>5384</t>
+        </is>
+      </c>
+      <c r="S62" s="2" t="inlineStr">
+        <is>
+          <t>2554</t>
+        </is>
+      </c>
+      <c r="T62" s="2" t="inlineStr">
+        <is>
+          <t>10499</t>
+        </is>
+      </c>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>0,74%</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="n"/>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>942</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>664738</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>664738</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>664738</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>977</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>761972</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>761972</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>761972</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr">
+        <is>
+          <t>1919</t>
+        </is>
+      </c>
+      <c r="R63" s="2" t="inlineStr">
+        <is>
+          <t>1426710</t>
+        </is>
+      </c>
+      <c r="S63" s="2" t="inlineStr">
+        <is>
+          <t>1426710</t>
+        </is>
+      </c>
+      <c r="T63" s="2" t="inlineStr">
+        <is>
+          <t>1426710</t>
+        </is>
+      </c>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -4092,14 +7512,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A16:A27"/>
-    <mergeCell ref="A40:A51"/>
-    <mergeCell ref="A4:A15"/>
-    <mergeCell ref="C1:G1"/>
-    <mergeCell ref="H1:L1"/>
-    <mergeCell ref="A28:A39"/>
+    <mergeCell ref="J1:P1"/>
+    <mergeCell ref="A4:A18"/>
+    <mergeCell ref="A34:A48"/>
+    <mergeCell ref="A19:A33"/>
+    <mergeCell ref="A49:A63"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="M1:Q1"/>
+    <mergeCell ref="Q1:W1"/>
+    <mergeCell ref="C1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/trans_orig/IP35_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP35_2023-Estudios-trans_orig.xlsx
@@ -1973,12 +1973,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>38264</t>
+          <t>38290</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>49081</t>
+          <t>49329</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1988,12 +1988,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>69,98%</t>
+          <t>70,03%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>89,76%</t>
+          <t>90,22%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2008,12 +2008,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>44319</t>
+          <t>43874</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>55549</t>
+          <t>55995</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2023,12 +2023,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>71,48%</t>
+          <t>70,76%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>89,59%</t>
+          <t>90,31%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2043,12 +2043,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>85279</t>
+          <t>86339</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>102199</t>
+          <t>101807</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2058,12 +2058,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>73,09%</t>
+          <t>74,0%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>87,59%</t>
+          <t>87,25%</t>
         </is>
       </c>
     </row>
@@ -2086,12 +2086,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4725</t>
+          <t>4205</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15233</t>
+          <t>14924</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2121,12 +2121,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4108</t>
+          <t>3622</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15002</t>
+          <t>14883</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2156,12 +2156,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11155</t>
+          <t>11146</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>27249</t>
+          <t>25200</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>21,6%</t>
         </is>
       </c>
     </row>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4850</t>
+          <t>5541</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2219,7 +2219,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2234,12 +2234,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>957</t>
+          <t>862</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6601</t>
+          <t>6676</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2269,12 +2269,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1677</t>
+          <t>1803</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>9014</t>
+          <t>8969</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,69%</t>
         </is>
       </c>
     </row>
@@ -2434,7 +2434,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2776</t>
+          <t>2129</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,7 +2449,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,7 +2469,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4444</t>
+          <t>4325</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4871</t>
+          <t>4952</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,7 +2519,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,51%</t>
         </is>
       </c>
     </row>
@@ -2999,7 +2999,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3316</t>
+          <t>3190</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3014,7 +3014,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2061</t>
+          <t>2166</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>9087</t>
+          <t>10410</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3064,12 +3064,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3012</t>
+          <t>2577</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>10856</t>
+          <t>10235</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -3107,12 +3107,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>74764</t>
+          <t>74341</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>110219</t>
+          <t>109091</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3122,12 +3122,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3142,12 +3142,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>66700</t>
+          <t>67482</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>101258</t>
+          <t>101061</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3177,12 +3177,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>152794</t>
+          <t>152867</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>203329</t>
+          <t>203103</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3197,7 +3197,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>20,79%</t>
         </is>
       </c>
     </row>
@@ -3220,12 +3220,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>63443</t>
+          <t>61280</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>96976</t>
+          <t>95502</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3235,12 +3235,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3255,12 +3255,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>57186</t>
+          <t>59298</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>91783</t>
+          <t>90713</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3290,12 +3290,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>129588</t>
+          <t>129521</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>174989</t>
+          <t>176818</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3310,7 +3310,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>18,1%</t>
         </is>
       </c>
     </row>
@@ -3333,12 +3333,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>30529</t>
+          <t>29781</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>53059</t>
+          <t>51594</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3348,12 +3348,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3368,12 +3368,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>55434</t>
+          <t>55438</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>83428</t>
+          <t>83049</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>91439</t>
+          <t>90535</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>128200</t>
+          <t>127347</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,03%</t>
         </is>
       </c>
     </row>
@@ -3446,12 +3446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>94082</t>
+          <t>96014</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>192273</t>
+          <t>187607</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3461,12 +3461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>41,75%</t>
+          <t>40,74%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>94979</t>
+          <t>94183</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>147654</t>
+          <t>145804</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>201609</t>
+          <t>200510</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>306161</t>
+          <t>309970</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>31,72%</t>
         </is>
       </c>
     </row>
@@ -3559,12 +3559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>92838</t>
+          <t>95864</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>136126</t>
+          <t>137294</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3574,12 +3574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>29,81%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>138130</t>
+          <t>139911</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>184171</t>
+          <t>182531</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3609,12 +3609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>35,33%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>251541</t>
+          <t>247499</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>311643</t>
+          <t>309540</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3644,12 +3644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>31,89%</t>
+          <t>31,68%</t>
         </is>
       </c>
     </row>
@@ -3672,12 +3672,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>1231</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>8067</t>
+          <t>8362</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3692,7 +3692,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3385</t>
+          <t>3115</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>16117</t>
+          <t>16632</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>6018</t>
+          <t>5846</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>20289</t>
+          <t>19816</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -3785,12 +3785,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>497</t>
+          <t>477</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>5397</t>
+          <t>5055</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3800,12 +3800,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3820,12 +3820,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>347</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>4996</t>
+          <t>4805</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3855,12 +3855,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1377</t>
+          <t>1358</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>8370</t>
+          <t>7918</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,81%</t>
         </is>
       </c>
     </row>
@@ -3903,7 +3903,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2091</t>
+          <t>2131</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3918,7 +3918,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2914</t>
+          <t>2903</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3973,7 +3973,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>3541</t>
+          <t>3871</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3988,7 +3988,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,4%</t>
         </is>
       </c>
     </row>
@@ -4241,12 +4241,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>1291</t>
+          <t>1377</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>7691</t>
+          <t>7699</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4256,12 +4256,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4276,12 +4276,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>1277</t>
+          <t>1191</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>9376</t>
+          <t>8845</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4291,12 +4291,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4311,12 +4311,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>3675</t>
+          <t>3846</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>12999</t>
+          <t>13373</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,02%</t>
         </is>
       </c>
     </row>
@@ -4354,12 +4354,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>68488</t>
+          <t>69438</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>89164</t>
+          <t>89236</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4369,12 +4369,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>45,8%</t>
+          <t>46,43%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>59,62%</t>
+          <t>59,67%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>91979</t>
+          <t>90440</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>115436</t>
+          <t>115364</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4404,12 +4404,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>50,17%</t>
+          <t>49,33%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>62,96%</t>
+          <t>62,92%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>164459</t>
+          <t>166518</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>196065</t>
+          <t>197973</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4439,12 +4439,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>49,4%</t>
+          <t>50,02%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>58,9%</t>
+          <t>59,47%</t>
         </is>
       </c>
     </row>
@@ -4467,12 +4467,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>43353</t>
+          <t>43968</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>63422</t>
+          <t>61972</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4482,82 +4482,82 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
+          <t>29,4%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>41,44%</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>58539</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>45824</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>70215</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>31,93%</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>24,99%</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>38,3%</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>111433</t>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t>96516</t>
+        </is>
+      </c>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>126613</t>
+        </is>
+      </c>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>33,47%</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
           <t>28,99%</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>42,41%</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>58539</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>47241</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t>69005</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr">
-        <is>
-          <t>31,93%</t>
-        </is>
-      </c>
-      <c r="O37" s="2" t="inlineStr">
-        <is>
-          <t>25,77%</t>
-        </is>
-      </c>
-      <c r="P37" s="2" t="inlineStr">
-        <is>
-          <t>37,64%</t>
-        </is>
-      </c>
-      <c r="Q37" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="R37" s="2" t="inlineStr">
-        <is>
-          <t>111433</t>
-        </is>
-      </c>
-      <c r="S37" s="2" t="inlineStr">
-        <is>
-          <t>97431</t>
-        </is>
-      </c>
-      <c r="T37" s="2" t="inlineStr">
-        <is>
-          <t>126620</t>
-        </is>
-      </c>
-      <c r="U37" s="2" t="inlineStr">
-        <is>
-          <t>33,47%</t>
-        </is>
-      </c>
-      <c r="V37" s="2" t="inlineStr">
-        <is>
-          <t>29,27%</t>
-        </is>
-      </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>38,04%</t>
+          <t>38,03%</t>
         </is>
       </c>
     </row>
@@ -4580,12 +4580,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>7041</t>
+          <t>6943</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>16778</t>
+          <t>16619</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>9109</t>
+          <t>9323</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>22145</t>
+          <t>23048</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4630,12 +4630,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>18951</t>
+          <t>18487</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>34663</t>
+          <t>35423</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4665,12 +4665,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,64%</t>
         </is>
       </c>
     </row>
@@ -4733,7 +4733,7 @@
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>3452</t>
+          <t>2695</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4748,7 +4748,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>2874</t>
+          <t>2933</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4783,7 +4783,7 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,88%</t>
         </is>
       </c>
     </row>
@@ -4846,7 +4846,7 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>5400</t>
+          <t>4947</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4881,7 +4881,7 @@
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>5745</t>
+          <t>5640</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,69%</t>
         </is>
       </c>
     </row>
@@ -4924,7 +4924,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>3331</t>
+          <t>2942</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4939,7 +4939,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>3507</t>
+          <t>2659</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5009,7 +5009,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,8%</t>
         </is>
       </c>
     </row>
@@ -5185,7 +5185,7 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>4351</t>
+          <t>4079</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5200,7 +5200,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5220,7 +5220,7 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>4276</t>
+          <t>4280</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5235,7 +5235,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -5258,12 +5258,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>512</t>
+          <t>510</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>5581</t>
+          <t>4931</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5278,7 +5278,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>512</t>
+          <t>505</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>5561</t>
+          <t>5178</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5348,7 +5348,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,56%</t>
         </is>
       </c>
     </row>
@@ -5376,7 +5376,7 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>3671</t>
+          <t>3521</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5391,7 +5391,7 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5446,7 +5446,7 @@
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>3619</t>
+          <t>3742</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5461,7 +5461,7 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,12%</t>
         </is>
       </c>
     </row>
@@ -5832,7 +5832,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>2582</t>
+          <t>2477</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5847,7 +5847,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5867,7 +5867,7 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>4361</t>
+          <t>4863</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5882,7 +5882,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5902,7 +5902,7 @@
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>5377</t>
+          <t>5112</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5917,7 +5917,7 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,36%</t>
         </is>
       </c>
     </row>
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>1161</t>
+          <t>1325</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>7525</t>
+          <t>7493</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5955,7 +5955,7 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
@@ -5975,12 +5975,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>1169</t>
+          <t>1244</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>9088</t>
+          <t>8683</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -5990,12 +5990,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6010,12 +6010,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>3599</t>
+          <t>3562</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>12874</t>
+          <t>13355</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6030,7 +6030,7 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -6053,12 +6053,12 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>64303</t>
+          <t>63361</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>95848</t>
+          <t>94175</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>85977</t>
+          <t>84300</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>126235</t>
+          <t>123240</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6103,12 +6103,12 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6123,12 +6123,12 @@
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>157042</t>
+          <t>158994</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>206400</t>
+          <t>207034</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -6138,12 +6138,12 @@
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,51%</t>
         </is>
       </c>
     </row>
@@ -6166,12 +6166,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>41326</t>
+          <t>40614</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>66081</t>
+          <t>65489</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>46768</t>
+          <t>46001</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>74403</t>
+          <t>74949</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6216,12 +6216,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6236,12 +6236,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>94889</t>
+          <t>95445</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>131304</t>
+          <t>130783</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6251,12 +6251,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,17%</t>
         </is>
       </c>
     </row>
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>6945</t>
+          <t>6555</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>17458</t>
+          <t>16295</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6314,12 +6314,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>8854</t>
+          <t>9083</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>23196</t>
+          <t>23252</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6329,12 +6329,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6349,12 +6349,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>18633</t>
+          <t>19529</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>36972</t>
+          <t>36168</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6364,12 +6364,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -6397,7 +6397,7 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>2853</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6412,7 +6412,7 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6427,12 +6427,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>2638</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>10593</t>
+          <t>10019</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6442,12 +6442,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6462,12 +6462,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>3297</t>
+          <t>3331</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>11672</t>
+          <t>11694</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>77009</t>
+          <t>75975</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>111011</t>
+          <t>110896</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6520,12 +6520,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6540,12 +6540,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>70363</t>
+          <t>69582</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>104241</t>
+          <t>104907</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6555,12 +6555,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6575,12 +6575,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>154625</t>
+          <t>155580</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>203407</t>
+          <t>202584</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6590,12 +6590,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,2%</t>
         </is>
       </c>
     </row>
@@ -6618,12 +6618,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>63604</t>
+          <t>64875</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>96272</t>
+          <t>96169</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6633,12 +6633,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6653,12 +6653,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>60125</t>
+          <t>59276</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>92968</t>
+          <t>90632</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6668,12 +6668,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6688,12 +6688,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>131214</t>
+          <t>132047</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>177486</t>
+          <t>178201</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6703,12 +6703,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,49%</t>
         </is>
       </c>
     </row>
@@ -6731,12 +6731,12 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>29735</t>
+          <t>31773</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>51794</t>
+          <t>52611</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -6746,12 +6746,12 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -6766,12 +6766,12 @@
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>54608</t>
+          <t>53631</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>84434</t>
+          <t>83478</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -6781,12 +6781,12 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -6801,12 +6801,12 @@
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>91750</t>
+          <t>90496</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>127591</t>
+          <t>128065</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
@@ -6816,12 +6816,12 @@
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,98%</t>
         </is>
       </c>
     </row>
@@ -6844,12 +6844,12 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>92745</t>
+          <t>93404</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>195311</t>
+          <t>194431</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -6859,12 +6859,12 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -6879,12 +6879,12 @@
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>93957</t>
+          <t>94479</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>151219</t>
+          <t>150271</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -6914,12 +6914,12 @@
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>199766</t>
+          <t>201855</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>323799</t>
+          <t>308942</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
@@ -6929,12 +6929,12 @@
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>21,65%</t>
         </is>
       </c>
     </row>
@@ -6957,12 +6957,12 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>99893</t>
+          <t>99613</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>138091</t>
+          <t>138386</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -6972,12 +6972,12 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -6992,12 +6992,12 @@
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>138180</t>
+          <t>139247</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>183911</t>
+          <t>189863</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -7007,12 +7007,12 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7027,12 +7027,12 @@
       </c>
       <c r="S59" s="2" t="inlineStr">
         <is>
-          <t>251117</t>
+          <t>251966</t>
         </is>
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>313341</t>
+          <t>311459</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
@@ -7042,12 +7042,12 @@
       </c>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>21,83%</t>
         </is>
       </c>
     </row>
@@ -7070,12 +7070,12 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>36365</t>
+          <t>36402</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>72500</t>
+          <t>73144</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -7085,12 +7085,12 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -7105,12 +7105,12 @@
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>46947</t>
+          <t>45709</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>73989</t>
+          <t>75013</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -7120,12 +7120,12 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7140,12 +7140,12 @@
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>88996</t>
+          <t>88388</t>
         </is>
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>133332</t>
+          <t>136719</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
@@ -7155,12 +7155,12 @@
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,58%</t>
         </is>
       </c>
     </row>
@@ -7183,12 +7183,12 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>5982</t>
+          <t>6070</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>16878</t>
+          <t>17380</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -7198,12 +7198,12 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -7218,12 +7218,12 @@
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>5387</t>
+          <t>5830</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>18568</t>
+          <t>18478</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -7233,12 +7233,12 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>13912</t>
+          <t>14174</t>
         </is>
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>30894</t>
+          <t>32278</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
@@ -7268,12 +7268,12 @@
       </c>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,26%</t>
         </is>
       </c>
     </row>
@@ -7296,12 +7296,12 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>496</t>
+          <t>483</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>5544</t>
+          <t>5258</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -7316,7 +7316,7 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -7331,12 +7331,12 @@
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>1206</t>
+          <t>1165</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>7591</t>
+          <t>7752</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -7346,12 +7346,12 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>2554</t>
+          <t>2560</t>
         </is>
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>10499</t>
+          <t>10331</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
@@ -7386,7 +7386,7 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,72%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP35_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP35_2023-Estudios-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -1963,72 +1963,72 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>47689</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>41925</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>51484</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>84,06%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>73,9%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>90,75%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>44584</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>38290</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>49329</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>81,54%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>70,03%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>90,22%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>50960</t>
+          <t>36629</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>43874</t>
+          <t>29977</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>55995</t>
+          <t>40571</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>82,19%</t>
+          <t>78,34%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>70,76%</t>
+          <t>64,11%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>90,31%</t>
+          <t>86,77%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2038,32 +2038,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>95544</t>
+          <t>84318</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>86339</t>
+          <t>76478</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>101807</t>
+          <t>90384</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>81,88%</t>
+          <t>81,47%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>74,0%</t>
+          <t>73,9%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>87,25%</t>
+          <t>87,34%</t>
         </is>
       </c>
     </row>
@@ -2076,72 +2076,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>6613</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>3204</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>12207</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>11,66%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>5,65%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>21,52%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>8590</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>4205</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>14924</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>15,71%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>7,69%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>27,29%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>8229</t>
+          <t>8870</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3622</t>
+          <t>5249</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14883</t>
+          <t>15362</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>32,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2151,32 +2151,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>16818</t>
+          <t>15483</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11146</t>
+          <t>10064</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>25200</t>
+          <t>24766</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>23,93%</t>
         </is>
       </c>
     </row>
@@ -2189,72 +2189,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>2429</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>820</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>5664</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>4,28%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>1,45%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>9,98%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>1504</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>5541</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>2,75%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>10,13%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2816</t>
+          <t>1259</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>862</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6676</t>
+          <t>4094</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2264,32 +2264,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>4320</t>
+          <t>3688</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1803</t>
+          <t>1520</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>8969</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>6,97%</t>
         </is>
       </c>
     </row>
@@ -2302,74 +2302,74 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>46758</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>46758</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>46758</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="O18" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="P18" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>62004</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>62004</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>62004</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
           <t>152</t>
@@ -2377,17 +2377,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>492</t>
+          <t>907</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2434,12 +2434,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2129</t>
+          <t>4948</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -2449,7 +2449,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>868</t>
+          <t>422</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4325</t>
+          <t>2625</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2494,7 +2494,7 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1360</t>
+          <t>1328</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4952</t>
+          <t>5181</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
@@ -2519,7 +2519,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,57%</t>
         </is>
       </c>
     </row>
@@ -2984,72 +2984,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>4801</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>2107</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>9006</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>1,01%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>1,89%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>896</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>3190</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>0,69%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>4886</t>
+          <t>873</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2166</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>10410</t>
+          <t>3574</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3059,32 +3059,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>5782</t>
+          <t>5674</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2577</t>
+          <t>2611</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>10235</t>
+          <t>10646</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -3097,72 +3097,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>78672</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>65330</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>96204</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>16,54%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>13,73%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>20,22%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>140</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>93255</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>74341</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>109091</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>20,25%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>16,14%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>23,69%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>83651</t>
+          <t>94465</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>67482</t>
+          <t>80225</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>101061</t>
+          <t>111321</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3172,32 +3172,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>176906</t>
+          <t>173138</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>152867</t>
+          <t>150632</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>203103</t>
+          <t>196070</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>21,59%</t>
         </is>
       </c>
     </row>
@@ -3210,72 +3210,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>68866</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>54578</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>86202</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>14,48%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>11,47%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>18,12%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>79166</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>61280</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>95502</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>17,19%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>13,31%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>20,74%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>72992</t>
+          <t>75432</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>59298</t>
+          <t>61697</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>90713</t>
+          <t>89645</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3285,32 +3285,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>152158</t>
+          <t>144299</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>129521</t>
+          <t>126610</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>176818</t>
+          <t>165247</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,2%</t>
         </is>
       </c>
     </row>
@@ -3323,72 +3323,72 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>62868</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>50290</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>77216</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>13,22%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>10,57%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>16,23%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>40816</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>29781</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>51594</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>8,86%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>6,47%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>11,2%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>67903</t>
+          <t>40766</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>55438</t>
+          <t>32166</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>83049</t>
+          <t>52627</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3398,32 +3398,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>108720</t>
+          <t>103634</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>90535</t>
+          <t>87844</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>127347</t>
+          <t>121065</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>13,33%</t>
         </is>
       </c>
     </row>
@@ -3436,72 +3436,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>97319</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>82158</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>122380</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>20,46%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>17,27%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>25,73%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>148</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>121501</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>96014</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>187607</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>26,38%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>20,85%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>40,74%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>147</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>115042</t>
+          <t>92500</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>94183</t>
+          <t>78664</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>145804</t>
+          <t>108212</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3511,32 +3511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>236543</t>
+          <t>189819</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>200510</t>
+          <t>169139</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>309970</t>
+          <t>217734</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>23,98%</t>
         </is>
       </c>
     </row>
@@ -3549,72 +3549,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>152630</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>132704</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>172215</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>32,09%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>27,9%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>36,2%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>171</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>118565</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>95864</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>137294</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>25,75%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>20,82%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>29,81%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>187</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>161192</t>
+          <t>121927</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>139911</t>
+          <t>105790</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>182531</t>
+          <t>138395</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>24,46%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>35,33%</t>
+          <t>32,0%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3624,32 +3624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>279756</t>
+          <t>274556</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>247499</t>
+          <t>248831</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>309540</t>
+          <t>301026</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>30,23%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>27,4%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>31,68%</t>
+          <t>33,15%</t>
         </is>
       </c>
     </row>
@@ -3662,72 +3662,72 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>7642</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>3549</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>15407</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>1,61%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>0,75%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>3,24%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>3426</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>1231</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>8362</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>0,74%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>1,82%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>7795</t>
+          <t>3575</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3115</t>
+          <t>1107</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>16632</t>
+          <t>8152</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3737,32 +3737,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>11221</t>
+          <t>11216</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>5846</t>
+          <t>5932</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>19816</t>
+          <t>19861</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -3780,32 +3780,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>1902</t>
+          <t>1495</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>477</t>
+          <t>249</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>5055</t>
+          <t>4830</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3815,32 +3815,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>1717</t>
+          <t>2068</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>347</t>
+          <t>582</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>4805</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3850,27 +3850,27 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>3618</t>
+          <t>3562</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1358</t>
+          <t>1387</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>7918</t>
+          <t>7359</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -3893,7 +3893,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>492</t>
+          <t>479</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -3903,12 +3903,12 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2131</t>
+          <t>2210</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>573</t>
+          <t>422</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -3938,12 +3938,12 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2903</t>
+          <t>2456</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
@@ -3953,7 +3953,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3963,7 +3963,7 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>1064</t>
+          <t>900</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
@@ -3973,12 +3973,12 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>3871</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
@@ -3988,7 +3988,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,33%</t>
         </is>
       </c>
     </row>
@@ -4001,74 +4001,74 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>475678</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>475678</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>475678</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
           <t>643</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>460510</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>460510</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>460510</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>432448</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>432448</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>432448</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="O33" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr">
+      <c r="P33" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>656</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>516619</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="inlineStr">
-        <is>
-          <t>516619</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr">
-        <is>
-          <t>516619</t>
-        </is>
-      </c>
-      <c r="N33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
           <t>1299</t>
@@ -4076,17 +4076,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>977129</t>
+          <t>908126</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>977129</t>
+          <t>908126</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>977129</t>
+          <t>908126</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4231,72 +4231,72 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>3697</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>997</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>8320</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>2,19%</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>0,59%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>4,94%</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>3352</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>1377</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>7699</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>2,24%</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>0,92%</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>5,15%</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>3792</t>
+          <t>3483</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>1191</t>
+          <t>1238</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>8845</t>
+          <t>7556</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4306,32 +4306,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>7145</t>
+          <t>7179</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>3846</t>
+          <t>3771</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>13373</t>
+          <t>12898</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,05%</t>
         </is>
       </c>
     </row>
@@ -4344,107 +4344,107 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>94977</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>83442</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>105115</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>56,39%</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>49,54%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>62,41%</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
           <t>115</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>79122</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>69438</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>89236</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>52,91%</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>46,43%</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>79962</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>68018</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>89077</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>53,32%</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>45,35%</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>59,39%</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>174939</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t>160487</t>
+        </is>
+      </c>
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t>189989</t>
+        </is>
+      </c>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>54,94%</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>50,41%</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
         <is>
           <t>59,67%</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>103094</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="inlineStr">
-        <is>
-          <t>90440</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr">
-        <is>
-          <t>115364</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr">
-        <is>
-          <t>56,23%</t>
-        </is>
-      </c>
-      <c r="O36" s="2" t="inlineStr">
-        <is>
-          <t>49,33%</t>
-        </is>
-      </c>
-      <c r="P36" s="2" t="inlineStr">
-        <is>
-          <t>62,92%</t>
-        </is>
-      </c>
-      <c r="Q36" s="2" t="inlineStr">
-        <is>
-          <t>242</t>
-        </is>
-      </c>
-      <c r="R36" s="2" t="inlineStr">
-        <is>
-          <t>182216</t>
-        </is>
-      </c>
-      <c r="S36" s="2" t="inlineStr">
-        <is>
-          <t>166518</t>
-        </is>
-      </c>
-      <c r="T36" s="2" t="inlineStr">
-        <is>
-          <t>197973</t>
-        </is>
-      </c>
-      <c r="U36" s="2" t="inlineStr">
-        <is>
-          <t>54,74%</t>
-        </is>
-      </c>
-      <c r="V36" s="2" t="inlineStr">
-        <is>
-          <t>50,02%</t>
-        </is>
-      </c>
-      <c r="W36" s="2" t="inlineStr">
-        <is>
-          <t>59,47%</t>
         </is>
       </c>
     </row>
@@ -4457,72 +4457,72 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>53186</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>43416</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>64339</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>31,58%</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>25,78%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>38,2%</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>52894</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>43968</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>61972</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>35,37%</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>29,4%</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>41,44%</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>58539</t>
+          <t>52227</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>45824</t>
+          <t>42427</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>70215</t>
+          <t>62078</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>34,82%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>38,3%</t>
+          <t>41,39%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4532,32 +4532,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>111433</t>
+          <t>105413</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>96516</t>
+          <t>90925</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>126613</t>
+          <t>118858</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>33,11%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>28,56%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>38,03%</t>
+          <t>37,33%</t>
         </is>
       </c>
     </row>
@@ -4570,72 +4570,72 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>13935</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>8592</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>21778</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>8,27%</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>5,1%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>12,93%</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>11026</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>6943</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>16619</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>7,37%</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>4,64%</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>11,11%</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>14895</t>
+          <t>11041</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>9323</t>
+          <t>7009</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>23048</t>
+          <t>16955</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4645,32 +4645,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>25921</t>
+          <t>24976</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>18487</t>
+          <t>17393</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>35423</t>
+          <t>33396</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,49%</t>
         </is>
       </c>
     </row>
@@ -4683,82 +4683,82 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>559</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2970</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K39" s="2" t="inlineStr">
-        <is>
-          <t>573</t>
-        </is>
-      </c>
-      <c r="L39" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr">
-        <is>
-          <t>2695</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="inlineStr">
-        <is>
-          <t>0,31%</t>
-        </is>
-      </c>
-      <c r="O39" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P39" s="2" t="inlineStr">
-        <is>
-          <t>1,47%</t>
-        </is>
-      </c>
-      <c r="Q39" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>573</t>
+          <t>559</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
@@ -4768,12 +4768,12 @@
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>2933</t>
+          <t>2804</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
@@ -4796,82 +4796,82 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1423</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4972</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>1605</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>4947</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>0,88%</t>
-        </is>
-      </c>
-      <c r="O40" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P40" s="2" t="inlineStr">
-        <is>
-          <t>2,7%</t>
-        </is>
-      </c>
-      <c r="Q40" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>1605</t>
+          <t>1423</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
@@ -4881,12 +4881,12 @@
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>5640</t>
+          <t>5410</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,7%</t>
         </is>
       </c>
     </row>
@@ -4909,72 +4909,72 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>566</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>2942</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>1,97%</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>492</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3041</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -4984,7 +4984,7 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>566</t>
+          <t>492</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
@@ -4994,12 +4994,12 @@
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>2659</t>
+          <t>2438</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
@@ -5009,7 +5009,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,77%</t>
         </is>
       </c>
     </row>
@@ -5135,82 +5135,82 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>641</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3002</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t>851</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr">
-        <is>
-          <t>4079</t>
-        </is>
-      </c>
-      <c r="N43" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
-      <c r="O43" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P43" s="2" t="inlineStr">
-        <is>
-          <t>2,22%</t>
-        </is>
-      </c>
-      <c r="Q43" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>851</t>
+          <t>641</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>4280</t>
+          <t>3291</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
@@ -5235,7 +5235,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,03%</t>
         </is>
       </c>
     </row>
@@ -5248,72 +5248,72 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>1853</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>510</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>4931</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>1,24%</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>3,3%</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>566</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5562</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5323,32 +5323,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>1853</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>505</t>
+          <t>557</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>5178</t>
+          <t>5425</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,7%</t>
         </is>
       </c>
     </row>
@@ -5361,72 +5361,72 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>738</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>3521</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>2,35%</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>767</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5393</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5436,7 +5436,7 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>738</t>
+          <t>767</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>3742</t>
+          <t>3825</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
@@ -5461,7 +5461,7 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,2%</t>
         </is>
       </c>
     </row>
@@ -5700,74 +5700,74 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>149976</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>149976</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>149976</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="O48" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr">
+      <c r="P48" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>238</t>
-        </is>
-      </c>
-      <c r="K48" s="2" t="inlineStr">
-        <is>
-          <t>183349</t>
-        </is>
-      </c>
-      <c r="L48" s="2" t="inlineStr">
-        <is>
-          <t>183349</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr">
-        <is>
-          <t>183349</t>
-        </is>
-      </c>
-      <c r="N48" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O48" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P48" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q48" s="2" t="inlineStr">
         <is>
           <t>468</t>
@@ -5775,17 +5775,17 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>332900</t>
+          <t>318395</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>332900</t>
+          <t>318395</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>332900</t>
+          <t>318395</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5822,7 +5822,7 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>492</t>
+          <t>907</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -5832,49 +5832,49 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>2477</t>
+          <t>4778</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
+          <t>0,13%</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>0,68%</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>422</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>2755</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
           <t>0,07%</t>
         </is>
       </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="J49" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K49" s="2" t="inlineStr">
-        <is>
-          <t>868</t>
-        </is>
-      </c>
-      <c r="L49" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr">
-        <is>
-          <t>4863</t>
-        </is>
-      </c>
-      <c r="N49" s="2" t="inlineStr">
-        <is>
-          <t>0,11%</t>
-        </is>
-      </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
@@ -5882,7 +5882,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5892,7 +5892,7 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>1360</t>
+          <t>1328</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
@@ -5902,7 +5902,7 @@
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>5112</t>
+          <t>4818</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5930,72 +5930,72 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>3697</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>1188</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>8510</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>0,53%</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>1,21%</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>3352</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>1325</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>7493</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="inlineStr">
-        <is>
-          <t>0,5%</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>1,13%</t>
-        </is>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>3792</t>
+          <t>3483</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>1244</t>
+          <t>1319</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>8683</t>
+          <t>7804</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6005,32 +6005,32 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>7145</t>
+          <t>7179</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>3562</t>
+          <t>3670</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>13355</t>
+          <t>13593</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,02%</t>
         </is>
       </c>
     </row>
@@ -6043,72 +6043,72 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>94977</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>78488</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>112379</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>13,55%</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>11,2%</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>16,04%</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
           <t>115</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>79122</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>63361</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>94175</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="inlineStr">
-        <is>
-          <t>11,9%</t>
-        </is>
-      </c>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t>9,53%</t>
-        </is>
-      </c>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>14,17%</t>
-        </is>
-      </c>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>103093</t>
+          <t>79962</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>84300</t>
+          <t>66712</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>123240</t>
+          <t>94657</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6118,32 +6118,32 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>182216</t>
+          <t>174939</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>158994</t>
+          <t>154056</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>207034</t>
+          <t>197786</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,87%</t>
         </is>
       </c>
     </row>
@@ -6156,72 +6156,72 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>53186</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>42266</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>66762</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>7,59%</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>6,03%</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>9,53%</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>52894</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>40614</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>65489</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="inlineStr">
-        <is>
-          <t>7,96%</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>6,11%</t>
-        </is>
-      </c>
-      <c r="I52" s="2" t="inlineStr">
-        <is>
-          <t>9,85%</t>
-        </is>
-      </c>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>58539</t>
+          <t>52228</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>46001</t>
+          <t>42909</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>74949</t>
+          <t>64994</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6231,32 +6231,32 @@
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>111433</t>
+          <t>105413</t>
         </is>
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>95445</t>
+          <t>89714</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>130783</t>
+          <t>123577</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,29%</t>
         </is>
       </c>
     </row>
@@ -6269,72 +6269,72 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>13935</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>8406</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>21203</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>1,99%</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>1,2%</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>3,03%</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>11026</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>6555</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>16295</t>
-        </is>
-      </c>
-      <c r="G53" s="2" t="inlineStr">
-        <is>
-          <t>1,66%</t>
-        </is>
-      </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>0,99%</t>
-        </is>
-      </c>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t>2,45%</t>
-        </is>
-      </c>
-      <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>14895</t>
+          <t>11041</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>9083</t>
+          <t>6980</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>23252</t>
+          <t>16868</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6344,32 +6344,32 @@
       </c>
       <c r="R53" s="2" t="inlineStr">
         <is>
-          <t>25921</t>
+          <t>24976</t>
         </is>
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>19529</t>
+          <t>17872</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>36168</t>
+          <t>33606</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -6382,72 +6382,72 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>5361</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>2512</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>10324</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>0,76%</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>1,47%</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>896</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>2853</t>
-        </is>
-      </c>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
-          <t>0,13%</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I54" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>5459</t>
+          <t>873</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>10019</t>
+          <t>3436</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6457,32 +6457,32 @@
       </c>
       <c r="R54" s="2" t="inlineStr">
         <is>
-          <t>6355</t>
+          <t>6233</t>
         </is>
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>3331</t>
+          <t>3160</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>11694</t>
+          <t>10814</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,81%</t>
         </is>
       </c>
     </row>
@@ -6495,72 +6495,72 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>80095</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>64874</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>97551</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>11,43%</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>9,26%</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>13,92%</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
           <t>140</t>
         </is>
       </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>93255</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>75975</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>110896</t>
-        </is>
-      </c>
-      <c r="G55" s="2" t="inlineStr">
-        <is>
-          <t>14,03%</t>
-        </is>
-      </c>
-      <c r="H55" s="2" t="inlineStr">
-        <is>
-          <t>11,43%</t>
-        </is>
-      </c>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t>16,68%</t>
-        </is>
-      </c>
-      <c r="J55" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>85256</t>
+          <t>94465</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>69582</t>
+          <t>81539</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>104907</t>
+          <t>110726</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6570,32 +6570,32 @@
       </c>
       <c r="R55" s="2" t="inlineStr">
         <is>
-          <t>178511</t>
+          <t>174561</t>
         </is>
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>155580</t>
+          <t>153150</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>202584</t>
+          <t>198569</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,93%</t>
         </is>
       </c>
     </row>
@@ -6608,72 +6608,72 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>68866</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>55321</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>86896</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>9,83%</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>7,89%</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>12,4%</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
           <t>111</t>
         </is>
       </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>79731</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>64875</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>96169</t>
-        </is>
-      </c>
-      <c r="G56" s="2" t="inlineStr">
-        <is>
-          <t>11,99%</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>9,76%</t>
-        </is>
-      </c>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t>14,47%</t>
-        </is>
-      </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>72992</t>
+          <t>75925</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>59276</t>
+          <t>63193</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>90632</t>
+          <t>90801</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6683,32 +6683,32 @@
       </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
-          <t>152724</t>
+          <t>144791</t>
         </is>
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>132047</t>
+          <t>124289</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>178201</t>
+          <t>168228</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,65%</t>
         </is>
       </c>
     </row>
@@ -6721,72 +6721,72 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>62868</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>50546</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>75348</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>8,97%</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>7,21%</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>10,75%</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>40816</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>31773</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>52611</t>
-        </is>
-      </c>
-      <c r="G57" s="2" t="inlineStr">
-        <is>
-          <t>6,14%</t>
-        </is>
-      </c>
-      <c r="H57" s="2" t="inlineStr">
-        <is>
-          <t>4,78%</t>
-        </is>
-      </c>
-      <c r="I57" s="2" t="inlineStr">
-        <is>
-          <t>7,91%</t>
-        </is>
-      </c>
-      <c r="J57" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>67903</t>
+          <t>40766</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>53631</t>
+          <t>31584</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>83478</t>
+          <t>53206</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -6796,32 +6796,32 @@
       </c>
       <c r="R57" s="2" t="inlineStr">
         <is>
-          <t>108720</t>
+          <t>103634</t>
         </is>
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>90496</t>
+          <t>87786</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>128065</t>
+          <t>121702</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,15%</t>
         </is>
       </c>
     </row>
@@ -6839,32 +6839,32 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>121501</t>
+          <t>97961</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>93404</t>
+          <t>80930</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>194431</t>
+          <t>125601</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -6874,32 +6874,32 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>115893</t>
+          <t>92500</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>94479</t>
+          <t>77883</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>150271</t>
+          <t>107819</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -6909,32 +6909,32 @@
       </c>
       <c r="R58" s="2" t="inlineStr">
         <is>
-          <t>237394</t>
+          <t>190460</t>
         </is>
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>201855</t>
+          <t>167300</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>308942</t>
+          <t>220980</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>16,61%</t>
         </is>
       </c>
     </row>
@@ -6947,72 +6947,72 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>152630</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>131726</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>175624</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>21,78%</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>18,8%</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>25,06%</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
           <t>174</t>
         </is>
       </c>
-      <c r="D59" s="2" t="inlineStr">
-        <is>
-          <t>120417</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="inlineStr">
-        <is>
-          <t>99613</t>
-        </is>
-      </c>
-      <c r="F59" s="2" t="inlineStr">
-        <is>
-          <t>138386</t>
-        </is>
-      </c>
-      <c r="G59" s="2" t="inlineStr">
-        <is>
-          <t>18,12%</t>
-        </is>
-      </c>
-      <c r="H59" s="2" t="inlineStr">
-        <is>
-          <t>14,99%</t>
-        </is>
-      </c>
-      <c r="I59" s="2" t="inlineStr">
-        <is>
-          <t>20,82%</t>
-        </is>
-      </c>
-      <c r="J59" s="2" t="inlineStr">
-        <is>
-          <t>187</t>
-        </is>
-      </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>161192</t>
+          <t>123931</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>139247</t>
+          <t>106218</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>189863</t>
+          <t>143092</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7022,32 +7022,32 @@
       </c>
       <c r="R59" s="2" t="inlineStr">
         <is>
-          <t>281609</t>
+          <t>276561</t>
         </is>
       </c>
       <c r="S59" s="2" t="inlineStr">
         <is>
-          <t>251966</t>
+          <t>249960</t>
         </is>
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>311459</t>
+          <t>303842</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>22,85%</t>
         </is>
       </c>
     </row>
@@ -7060,72 +7060,72 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>55331</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>43860</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>70348</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>7,9%</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>6,26%</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>10,04%</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
           <t>59</t>
         </is>
       </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t>48748</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>36402</t>
-        </is>
-      </c>
-      <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t>73144</t>
-        </is>
-      </c>
-      <c r="G60" s="2" t="inlineStr">
-        <is>
-          <t>7,33%</t>
-        </is>
-      </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>5,48%</t>
-        </is>
-      </c>
-      <c r="I60" s="2" t="inlineStr">
-        <is>
-          <t>11,0%</t>
-        </is>
-      </c>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>58755</t>
+          <t>40970</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>45709</t>
+          <t>31428</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>75013</t>
+          <t>52540</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7135,32 +7135,32 @@
       </c>
       <c r="R60" s="2" t="inlineStr">
         <is>
-          <t>107503</t>
+          <t>96301</t>
         </is>
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>88388</t>
+          <t>81121</t>
         </is>
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>136719</t>
+          <t>114725</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>8,63%</t>
         </is>
       </c>
     </row>
@@ -7173,72 +7173,72 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>8108</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>4396</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>15428</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>1,16%</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>0,63%</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>2,2%</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D61" s="2" t="inlineStr">
-        <is>
-          <t>10492</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>6070</t>
-        </is>
-      </c>
-      <c r="F61" s="2" t="inlineStr">
-        <is>
-          <t>17380</t>
-        </is>
-      </c>
-      <c r="G61" s="2" t="inlineStr">
-        <is>
-          <t>1,58%</t>
-        </is>
-      </c>
-      <c r="H61" s="2" t="inlineStr">
-        <is>
-          <t>0,91%</t>
-        </is>
-      </c>
-      <c r="I61" s="2" t="inlineStr">
-        <is>
-          <t>2,61%</t>
-        </is>
-      </c>
-      <c r="J61" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>9945</t>
+          <t>10938</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>5830</t>
+          <t>6428</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>18478</t>
+          <t>19457</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7248,17 +7248,17 @@
       </c>
       <c r="R61" s="2" t="inlineStr">
         <is>
-          <t>20437</t>
+          <t>19046</t>
         </is>
       </c>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>14174</t>
+          <t>12283</t>
         </is>
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>32278</t>
+          <t>29678</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
@@ -7268,12 +7268,12 @@
       </c>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,23%</t>
         </is>
       </c>
     </row>
@@ -7286,72 +7286,72 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>2908</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>1150</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>7001</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>0,16%</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>1,0%</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D62" s="2" t="inlineStr">
-        <is>
-          <t>1996</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr">
-        <is>
-          <t>483</t>
-        </is>
-      </c>
-      <c r="F62" s="2" t="inlineStr">
-        <is>
-          <t>5258</t>
-        </is>
-      </c>
-      <c r="G62" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>1681</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>417</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>4370</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
         <is>
           <t>0,07%</t>
         </is>
       </c>
-      <c r="I62" s="2" t="inlineStr">
-        <is>
-          <t>0,79%</t>
-        </is>
-      </c>
-      <c r="J62" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K62" s="2" t="inlineStr">
-        <is>
-          <t>3388</t>
-        </is>
-      </c>
-      <c r="L62" s="2" t="inlineStr">
-        <is>
-          <t>1165</t>
-        </is>
-      </c>
-      <c r="M62" s="2" t="inlineStr">
-        <is>
-          <t>7752</t>
-        </is>
-      </c>
-      <c r="N62" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="O62" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7361,22 +7361,22 @@
       </c>
       <c r="R62" s="2" t="inlineStr">
         <is>
-          <t>5384</t>
+          <t>4589</t>
         </is>
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>2560</t>
+          <t>2348</t>
         </is>
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>10331</t>
+          <t>8613</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="V62" s="2" t="inlineStr">
@@ -7386,7 +7386,7 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,65%</t>
         </is>
       </c>
     </row>
@@ -7399,74 +7399,74 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
+          <t>977</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
           <t>942</t>
         </is>
       </c>
-      <c r="D63" s="2" t="inlineStr">
-        <is>
-          <t>664738</t>
-        </is>
-      </c>
-      <c r="E63" s="2" t="inlineStr">
-        <is>
-          <t>664738</t>
-        </is>
-      </c>
-      <c r="F63" s="2" t="inlineStr">
-        <is>
-          <t>664738</t>
-        </is>
-      </c>
-      <c r="G63" s="2" t="inlineStr">
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>629182</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>629182</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>629182</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="O63" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I63" s="2" t="inlineStr">
+      <c r="P63" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J63" s="2" t="inlineStr">
-        <is>
-          <t>977</t>
-        </is>
-      </c>
-      <c r="K63" s="2" t="inlineStr">
-        <is>
-          <t>761972</t>
-        </is>
-      </c>
-      <c r="L63" s="2" t="inlineStr">
-        <is>
-          <t>761972</t>
-        </is>
-      </c>
-      <c r="M63" s="2" t="inlineStr">
-        <is>
-          <t>761972</t>
-        </is>
-      </c>
-      <c r="N63" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O63" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P63" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q63" s="2" t="inlineStr">
         <is>
           <t>1919</t>
@@ -7474,17 +7474,17 @@
       </c>
       <c r="R63" s="2" t="inlineStr">
         <is>
-          <t>1426710</t>
+          <t>1330011</t>
         </is>
       </c>
       <c r="S63" s="2" t="inlineStr">
         <is>
-          <t>1426710</t>
+          <t>1330011</t>
         </is>
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>1426710</t>
+          <t>1330011</t>
         </is>
       </c>
       <c r="U63" s="2" t="inlineStr">
